--- a/blog/politics_in_academia/data_politics_in_academia.xlsx
+++ b/blog/politics_in_academia/data_politics_in_academia.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4507"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="11_0FD8AD92D49BA05FC02F9560FDA218939A1E2E96" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B3670660-8283-426F-863A-4B74D0E27921}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="3"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Effect on Society" sheetId="1" r:id="rId1"/>
-    <sheet name="Trust" sheetId="2" r:id="rId2"/>
-    <sheet name="Canada" sheetId="4" r:id="rId3"/>
-    <sheet name="Fields" sheetId="5" r:id="rId4"/>
+    <sheet name="Macdonald Laurier" sheetId="4" r:id="rId1"/>
+    <sheet name="Pew - Effect" sheetId="1" r:id="rId2"/>
+    <sheet name="Pew - Trust" sheetId="2" r:id="rId3"/>
+    <sheet name="Pew - Fields" sheetId="5" r:id="rId4"/>
+    <sheet name="UofA - Ideology" sheetId="6" r:id="rId5"/>
   </sheets>
   <calcPr calcId="125725"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="62">
   <si>
     <t>Response</t>
   </si>
@@ -191,13 +193,25 @@
   </si>
   <si>
     <t>Feb</t>
+  </si>
+  <si>
+    <t>Ideology</t>
+  </si>
+  <si>
+    <t>Far Left/Liberal</t>
+  </si>
+  <si>
+    <t>Middle-of-the-Road</t>
+  </si>
+  <si>
+    <t>Conservative/Far Right</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -226,22 +240,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -279,7 +302,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -313,6 +336,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -347,9 +371,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -522,15 +547,313 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:F15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1">
+        <v>1993</v>
+      </c>
+      <c r="D1">
+        <v>1997</v>
+      </c>
+      <c r="E1">
+        <v>2000</v>
+      </c>
+      <c r="F1">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2">
+        <v>41.5</v>
+      </c>
+      <c r="D2">
+        <v>46.5</v>
+      </c>
+      <c r="E2">
+        <v>41.9</v>
+      </c>
+      <c r="F2">
+        <v>42.9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3">
+        <v>30.1</v>
+      </c>
+      <c r="D3">
+        <v>28.4</v>
+      </c>
+      <c r="E3">
+        <v>29</v>
+      </c>
+      <c r="F3">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4">
+        <v>7.7</v>
+      </c>
+      <c r="D4">
+        <v>7.9</v>
+      </c>
+      <c r="E4">
+        <v>6.9</v>
+      </c>
+      <c r="F4">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5">
+        <v>2.7</v>
+      </c>
+      <c r="D5">
+        <v>2.1</v>
+      </c>
+      <c r="E5">
+        <v>5.9</v>
+      </c>
+      <c r="F5">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6">
+        <v>2.4</v>
+      </c>
+      <c r="D6">
+        <v>3.8</v>
+      </c>
+      <c r="E6">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="F6">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7">
+        <v>10.9</v>
+      </c>
+      <c r="D7">
+        <v>7.3</v>
+      </c>
+      <c r="E7">
+        <v>5.7</v>
+      </c>
+      <c r="F7">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8">
+        <v>4.7</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+      <c r="E8">
+        <v>5.4</v>
+      </c>
+      <c r="F8">
+        <v>6.9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9">
+        <v>41.3</v>
+      </c>
+      <c r="D9">
+        <v>38.5</v>
+      </c>
+      <c r="E9">
+        <v>40.799999999999997</v>
+      </c>
+      <c r="F9">
+        <v>32.6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" t="s">
+        <v>17</v>
+      </c>
+      <c r="C10">
+        <v>6.9</v>
+      </c>
+      <c r="D10">
+        <v>11</v>
+      </c>
+      <c r="E10">
+        <v>8.5</v>
+      </c>
+      <c r="F10">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11">
+        <v>13.5</v>
+      </c>
+      <c r="D11">
+        <v>10.7</v>
+      </c>
+      <c r="E11">
+        <v>10.7</v>
+      </c>
+      <c r="F11">
+        <v>7.6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12">
+        <v>3.6</v>
+      </c>
+      <c r="D12">
+        <v>1.6</v>
+      </c>
+      <c r="E12">
+        <v>2.2000000000000002</v>
+      </c>
+      <c r="F12">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13">
+        <v>18.7</v>
+      </c>
+      <c r="D13">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="E13">
+        <v>25.5</v>
+      </c>
+      <c r="F13">
+        <v>4.9000000000000004</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" t="s">
+        <v>17</v>
+      </c>
+      <c r="C14">
+        <v>16</v>
+      </c>
+      <c r="D14">
+        <v>18.8</v>
+      </c>
+      <c r="E14">
+        <v>12.2</v>
+      </c>
+      <c r="F14">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D16"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.140625" style="1"/>
-    <col min="3" max="3" width="27.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="1"/>
+    <col min="3" max="3" width="27.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -544,7 +867,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>55</v>
       </c>
@@ -558,7 +881,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -572,7 +895,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>57</v>
       </c>
@@ -586,7 +909,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -600,7 +923,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>15</v>
       </c>
@@ -614,7 +937,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>55</v>
       </c>
@@ -628,7 +951,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -642,7 +965,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>57</v>
       </c>
@@ -656,7 +979,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -670,7 +993,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -684,7 +1007,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -698,7 +1021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -712,7 +1035,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>57</v>
       </c>
@@ -726,7 +1049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -740,7 +1063,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>15</v>
       </c>
@@ -760,16 +1083,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:E22"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="13.85546875" customWidth="1"/>
-    <col min="4" max="4" width="24.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="24.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>9</v>
       </c>
@@ -786,7 +1109,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -803,7 +1126,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -820,7 +1143,7 @@
         <v>-12</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -837,7 +1160,7 @@
         <v>-15</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>13</v>
       </c>
@@ -854,7 +1177,7 @@
         <v>-22</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>14</v>
       </c>
@@ -871,7 +1194,7 @@
         <v>-23</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>15</v>
       </c>
@@ -888,29 +1211,29 @@
         <v>-27</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B8">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="C8" t="s">
         <v>8</v>
       </c>
       <c r="D8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E8">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>-23</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C9" t="s">
         <v>8</v>
@@ -919,12 +1242,12 @@
         <v>6</v>
       </c>
       <c r="E9">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B10">
         <v>2020</v>
@@ -939,12 +1262,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C11" t="s">
         <v>8</v>
@@ -953,15 +1276,15 @@
         <v>6</v>
       </c>
       <c r="E11">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="C12" t="s">
         <v>8</v>
@@ -970,15 +1293,15 @@
         <v>6</v>
       </c>
       <c r="E12">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="C13" t="s">
         <v>8</v>
@@ -987,49 +1310,49 @@
         <v>6</v>
       </c>
       <c r="E13">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B14">
-        <v>2019</v>
+        <v>2023</v>
       </c>
       <c r="C14" t="s">
         <v>8</v>
       </c>
       <c r="D14" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B15">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="C15" t="s">
         <v>8</v>
       </c>
       <c r="D15" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B16">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
@@ -1038,15 +1361,15 @@
         <v>7</v>
       </c>
       <c r="E16">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="C17" t="s">
         <v>8</v>
@@ -1058,12 +1381,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B18">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="C18" t="s">
         <v>8</v>
@@ -1072,15 +1395,15 @@
         <v>7</v>
       </c>
       <c r="E18">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B19">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C19" t="s">
         <v>8</v>
@@ -1089,305 +1412,58 @@
         <v>7</v>
       </c>
       <c r="E19">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20">
+        <v>2022</v>
+      </c>
+      <c r="C20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21">
+        <v>2023</v>
+      </c>
+      <c r="C21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21">
         <v>50</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C1">
-        <v>1993</v>
-      </c>
-      <c r="D1">
-        <v>1997</v>
-      </c>
-      <c r="E1">
-        <v>2000</v>
-      </c>
-      <c r="F1">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" t="s">
-        <v>24</v>
-      </c>
-      <c r="B2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C2">
-        <v>41.5</v>
-      </c>
-      <c r="D2">
-        <v>46.5</v>
-      </c>
-      <c r="E2">
-        <v>41.9</v>
-      </c>
-      <c r="F2">
-        <v>42.9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3">
-        <v>30.1</v>
-      </c>
-      <c r="D3">
-        <v>28.4</v>
-      </c>
-      <c r="E3">
-        <v>29</v>
-      </c>
-      <c r="F3">
-        <v>28.4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4">
-        <v>7.7</v>
-      </c>
-      <c r="D4">
-        <v>7.9</v>
-      </c>
-      <c r="E4">
-        <v>6.9</v>
-      </c>
-      <c r="F4">
-        <v>6.1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5">
-        <v>2.7</v>
-      </c>
-      <c r="D5">
-        <v>2.1</v>
-      </c>
-      <c r="E5">
-        <v>5.9</v>
-      </c>
-      <c r="F5">
-        <v>7.4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6">
-        <v>2.4</v>
-      </c>
-      <c r="D6">
-        <v>3.8</v>
-      </c>
-      <c r="E6">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="F6">
-        <v>1.3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" t="s">
-        <v>19</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7">
-        <v>10.9</v>
-      </c>
-      <c r="D7">
-        <v>7.3</v>
-      </c>
-      <c r="E7">
-        <v>5.7</v>
-      </c>
-      <c r="F7">
-        <v>7.1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8">
-        <v>4.7</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-      <c r="E8">
-        <v>5.4</v>
-      </c>
-      <c r="F8">
-        <v>6.9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" t="s">
-        <v>24</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>41.3</v>
-      </c>
-      <c r="D9">
-        <v>38.5</v>
-      </c>
-      <c r="E9">
-        <v>40.799999999999997</v>
-      </c>
-      <c r="F9">
-        <v>32.6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10">
-        <v>6.9</v>
-      </c>
-      <c r="D10">
-        <v>11</v>
-      </c>
-      <c r="E10">
-        <v>8.5</v>
-      </c>
-      <c r="F10">
-        <v>17.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11">
-        <v>13.5</v>
-      </c>
-      <c r="D11">
-        <v>10.7</v>
-      </c>
-      <c r="E11">
-        <v>10.7</v>
-      </c>
-      <c r="F11">
-        <v>7.6</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12">
-        <v>3.6</v>
-      </c>
-      <c r="D12">
-        <v>1.6</v>
-      </c>
-      <c r="E12">
-        <v>2.2000000000000002</v>
-      </c>
-      <c r="F12">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13">
-        <v>18.7</v>
-      </c>
-      <c r="D13">
-        <v>19.399999999999999</v>
-      </c>
-      <c r="E13">
-        <v>25.5</v>
-      </c>
-      <c r="F13">
-        <v>4.9000000000000004</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14">
-        <v>16</v>
-      </c>
-      <c r="D14">
-        <v>18.8</v>
-      </c>
-      <c r="E14">
-        <v>12.2</v>
-      </c>
-      <c r="F14">
-        <v>33.700000000000003</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" t="s">
-        <v>17</v>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22">
+        <v>2024</v>
+      </c>
+      <c r="C22" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -1396,16 +1472,16 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" customWidth="1"/>
+    <col min="1" max="1" width="14.6640625" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>54</v>
       </c>
@@ -1416,7 +1492,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>51</v>
       </c>
@@ -1427,7 +1503,7 @@
         <v>1.6</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -1438,7 +1514,7 @@
         <v>5.2</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>49</v>
       </c>
@@ -1449,7 +1525,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>48</v>
       </c>
@@ -1460,7 +1536,7 @@
         <v>5.5</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>47</v>
       </c>
@@ -1471,7 +1547,7 @@
         <v>5.6</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>46</v>
       </c>
@@ -1482,7 +1558,7 @@
         <v>6.2</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -1493,7 +1569,7 @@
         <v>6.3</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -1504,7 +1580,7 @@
         <v>8.1999999999999993</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>43</v>
       </c>
@@ -1515,7 +1591,7 @@
         <v>16.8</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>42</v>
       </c>
@@ -1526,7 +1602,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>41</v>
       </c>
@@ -1537,7 +1613,7 @@
         <v>17.5</v>
       </c>
     </row>
-    <row r="13" spans="1:3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>40</v>
       </c>
@@ -1548,7 +1624,7 @@
         <v>20.8</v>
       </c>
     </row>
-    <row r="14" spans="1:3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -1559,7 +1635,7 @@
         <v>21.1</v>
       </c>
     </row>
-    <row r="15" spans="1:3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>38</v>
       </c>
@@ -1570,7 +1646,7 @@
         <v>25.3</v>
       </c>
     </row>
-    <row r="16" spans="1:3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>37</v>
       </c>
@@ -1581,7 +1657,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>36</v>
       </c>
@@ -1592,7 +1668,7 @@
         <v>27.3</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>35</v>
       </c>
@@ -1603,7 +1679,7 @@
         <v>29.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>34</v>
       </c>
@@ -1614,7 +1690,7 @@
         <v>32.799999999999997</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>33</v>
       </c>
@@ -1625,7 +1701,7 @@
         <v>40.299999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -1636,7 +1712,7 @@
         <v>43.8</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>31</v>
       </c>
@@ -1647,7 +1723,7 @@
         <v>48.3</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1658,7 +1734,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>29</v>
       </c>
@@ -1669,7 +1745,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -1683,4 +1759,492 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:C43"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B2" s="2">
+        <v>1969</v>
+      </c>
+      <c r="C2">
+        <v>45.4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="2">
+        <v>1975</v>
+      </c>
+      <c r="C3">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="2">
+        <v>1984</v>
+      </c>
+      <c r="C4">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B5" s="2">
+        <v>1989</v>
+      </c>
+      <c r="C5">
+        <v>45.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" s="2">
+        <v>1992</v>
+      </c>
+      <c r="C6">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="2">
+        <v>1995</v>
+      </c>
+      <c r="C7">
+        <v>46.2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>59</v>
+      </c>
+      <c r="B8" s="2">
+        <v>1998</v>
+      </c>
+      <c r="C8">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C9">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>59</v>
+      </c>
+      <c r="B10" s="2">
+        <v>2004</v>
+      </c>
+      <c r="C10">
+        <v>55.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>59</v>
+      </c>
+      <c r="B11" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C11">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>59</v>
+      </c>
+      <c r="B12" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C12">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>59</v>
+      </c>
+      <c r="B13" s="2">
+        <v>2013</v>
+      </c>
+      <c r="C13">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>59</v>
+      </c>
+      <c r="B14" s="2">
+        <v>2016</v>
+      </c>
+      <c r="C14">
+        <v>59.8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>59</v>
+      </c>
+      <c r="B15" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C15">
+        <v>74.2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>60</v>
+      </c>
+      <c r="B16" s="2">
+        <v>1969</v>
+      </c>
+      <c r="C16">
+        <v>27.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B17" s="2">
+        <v>1975</v>
+      </c>
+      <c r="C17">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="2">
+        <v>1984</v>
+      </c>
+      <c r="C18">
+        <v>26.6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19" s="2">
+        <v>1989</v>
+      </c>
+      <c r="C19">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B20" s="2">
+        <v>1992</v>
+      </c>
+      <c r="C20">
+        <v>33.700000000000003</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>60</v>
+      </c>
+      <c r="B21" s="2">
+        <v>1995</v>
+      </c>
+      <c r="C21">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+      <c r="B22" s="2">
+        <v>1998</v>
+      </c>
+      <c r="C22">
+        <v>35.299999999999997</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C23">
+        <v>32.299999999999997</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>60</v>
+      </c>
+      <c r="B24" s="2">
+        <v>2004</v>
+      </c>
+      <c r="C24">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B25" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C25">
+        <v>28.4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>60</v>
+      </c>
+      <c r="B26" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C26">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>60</v>
+      </c>
+      <c r="B27" s="2">
+        <v>2013</v>
+      </c>
+      <c r="C27">
+        <v>27.4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="2">
+        <v>2016</v>
+      </c>
+      <c r="C28">
+        <v>28.1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C29">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B30" s="2">
+        <v>1969</v>
+      </c>
+      <c r="C30">
+        <v>27.5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="2">
+        <v>1975</v>
+      </c>
+      <c r="C31">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B32" s="2">
+        <v>1984</v>
+      </c>
+      <c r="C32">
+        <v>33.799999999999997</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B33" s="2">
+        <v>1989</v>
+      </c>
+      <c r="C33">
+        <v>16.100000000000001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>61</v>
+      </c>
+      <c r="B34" s="2">
+        <v>1992</v>
+      </c>
+      <c r="C34">
+        <v>20.100000000000001</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>61</v>
+      </c>
+      <c r="B35" s="2">
+        <v>1995</v>
+      </c>
+      <c r="C35">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>61</v>
+      </c>
+      <c r="B36" s="2">
+        <v>1998</v>
+      </c>
+      <c r="C36">
+        <v>17.100000000000001</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="B37" s="2">
+        <v>2001</v>
+      </c>
+      <c r="C37">
+        <v>16.600000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>61</v>
+      </c>
+      <c r="B38" s="2">
+        <v>2004</v>
+      </c>
+      <c r="C38">
+        <v>17.399999999999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>61</v>
+      </c>
+      <c r="B39" s="2">
+        <v>2007</v>
+      </c>
+      <c r="C39">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>61</v>
+      </c>
+      <c r="B40" s="2">
+        <v>2010</v>
+      </c>
+      <c r="C40">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>61</v>
+      </c>
+      <c r="B41" s="2">
+        <v>2013</v>
+      </c>
+      <c r="C41">
+        <v>12.8</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>61</v>
+      </c>
+      <c r="B42" s="2">
+        <v>2016</v>
+      </c>
+      <c r="C42">
+        <v>12.1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>61</v>
+      </c>
+      <c r="B43" s="2">
+        <v>2021</v>
+      </c>
+      <c r="C43">
+        <v>10.8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
 </file>